--- a/data/Ficha_19_DL1153_202605_Depresion.xlsx
+++ b/data/Ficha_19_DL1153_202605_Depresion.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="139" r:id="rId3"/>
+    <pivotCache cacheId="143" r:id="rId3"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -730,7 +730,7 @@
     <t>PERIODO: ENERO - MAYO 2026</t>
   </si>
   <si>
-    <t>FUENTE:  HISMINSA: 17/05/2026</t>
+    <t>FUENTE:  HISMINSA: 24/05/2026</t>
   </si>
 </sst>
 </file>
@@ -891,19 +891,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="36">
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0%"/>
-    </dxf>
+  <dxfs count="32">
     <dxf>
       <numFmt numFmtId="13" formatCode="0%"/>
     </dxf>
@@ -1314,7 +1302,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="TuSoft" refreshedDate="46160.523520833332" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="178">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="TuSoft" refreshedDate="46167.526506365743" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="178">
   <cacheSource type="worksheet">
     <worksheetSource name="Tabla1"/>
   </cacheSource>
@@ -3790,8 +3778,8 @@
     <d v="2025-09-04T00:00:00"/>
     <d v="2026-05-31T00:00:00"/>
     <n v="3"/>
-    <n v="1"/>
-    <n v="6"/>
+    <n v="2"/>
+    <n v="7"/>
     <n v="1"/>
     <n v="1"/>
     <n v="1"/>
@@ -4126,7 +4114,7 @@
     <d v="2025-08-12T00:00:00"/>
     <d v="2026-05-08T00:00:00"/>
     <n v="3"/>
-    <n v="2"/>
+    <n v="1"/>
     <n v="6"/>
     <n v="1"/>
     <n v="1"/>
@@ -5229,9 +5217,9 @@
     <s v="M"/>
     <d v="2025-08-23T00:00:00"/>
     <d v="2026-05-19T00:00:00"/>
-    <n v="5"/>
-    <n v="3"/>
-    <n v="12"/>
+    <n v="6"/>
+    <n v="4"/>
+    <n v="13"/>
     <n v="1"/>
     <n v="1"/>
     <n v="1"/>
@@ -5699,7 +5687,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="139" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="143" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="I8:M14" firstHeaderRow="0" firstDataRow="1" firstDataCol="2" rowPageCount="3" colPageCount="1"/>
   <pivotFields count="23">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -5816,7 +5804,7 @@
     <dataField name="Suma de Indicador" fld="22" baseField="0" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="33">
+    <format dxfId="29">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -5825,7 +5813,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="32">
+    <format dxfId="28">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -5845,7 +5833,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica1" cacheId="139" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica1" cacheId="143" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A8:F14" firstHeaderRow="0" firstDataRow="1" firstDataCol="3" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="23">
     <pivotField axis="axisPage" compact="0" outline="0" showAll="0">
@@ -5969,7 +5957,7 @@
     <dataField name="Suma de Indicador" fld="22" baseField="0" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="35">
+    <format dxfId="31">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -5978,7 +5966,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="34">
+    <format dxfId="30">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -5998,31 +5986,31 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:V179" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:V179" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
   <autoFilter ref="A1:V179"/>
   <tableColumns count="22">
-    <tableColumn id="1" name="Año" dataDxfId="29"/>
-    <tableColumn id="2" name="Mes" dataDxfId="28"/>
-    <tableColumn id="3" name="DEPARTAMENTO" dataDxfId="27"/>
-    <tableColumn id="4" name="PROVINCIA" dataDxfId="26"/>
-    <tableColumn id="5" name="DISTRITO" dataDxfId="25"/>
-    <tableColumn id="6" name="UBIGEO" dataDxfId="24"/>
-    <tableColumn id="7" name="ESTABLECIMIENTO" dataDxfId="23"/>
-    <tableColumn id="8" name="renaes" dataDxfId="22"/>
-    <tableColumn id="9" name="tipo_doc" dataDxfId="21"/>
-    <tableColumn id="10" name="num_doc" dataDxfId="20"/>
-    <tableColumn id="11" name="id_genero" dataDxfId="19"/>
-    <tableColumn id="12" name="fecha_diagnostico" dataDxfId="18"/>
-    <tableColumn id="13" name="fecha_fin_paquete" dataDxfId="17"/>
-    <tableColumn id="14" name="ATC_SM" dataDxfId="16"/>
-    <tableColumn id="15" name="ATC_PSICOEDUC" dataDxfId="15"/>
-    <tableColumn id="16" name="ATC_INTER_IND" dataDxfId="14"/>
-    <tableColumn id="17" name="CUMPLE_03_ATC_SALUD_MENTAL" dataDxfId="13"/>
-    <tableColumn id="18" name="CUMPLE_01_ATC_PSICOEDUCACION" dataDxfId="12"/>
-    <tableColumn id="19" name="CUMPLE_06_ATC_PSICOTERAPIA_INTER_INDIV" dataDxfId="11"/>
-    <tableColumn id="20" name="Denominador" dataDxfId="10"/>
-    <tableColumn id="21" name="Numerador" dataDxfId="9"/>
-    <tableColumn id="22" name="Excluye" dataDxfId="8"/>
+    <tableColumn id="1" name="Año" dataDxfId="25"/>
+    <tableColumn id="2" name="Mes" dataDxfId="24"/>
+    <tableColumn id="3" name="DEPARTAMENTO" dataDxfId="23"/>
+    <tableColumn id="4" name="PROVINCIA" dataDxfId="22"/>
+    <tableColumn id="5" name="DISTRITO" dataDxfId="21"/>
+    <tableColumn id="6" name="UBIGEO" dataDxfId="20"/>
+    <tableColumn id="7" name="ESTABLECIMIENTO" dataDxfId="19"/>
+    <tableColumn id="8" name="renaes" dataDxfId="18"/>
+    <tableColumn id="9" name="tipo_doc" dataDxfId="17"/>
+    <tableColumn id="10" name="num_doc" dataDxfId="16"/>
+    <tableColumn id="11" name="id_genero" dataDxfId="15"/>
+    <tableColumn id="12" name="fecha_diagnostico" dataDxfId="14"/>
+    <tableColumn id="13" name="fecha_fin_paquete" dataDxfId="13"/>
+    <tableColumn id="14" name="ATC_SM" dataDxfId="12"/>
+    <tableColumn id="15" name="ATC_PSICOEDUC" dataDxfId="11"/>
+    <tableColumn id="16" name="ATC_INTER_IND" dataDxfId="10"/>
+    <tableColumn id="17" name="CUMPLE_03_ATC_SALUD_MENTAL" dataDxfId="9"/>
+    <tableColumn id="18" name="CUMPLE_01_ATC_PSICOEDUCACION" dataDxfId="8"/>
+    <tableColumn id="19" name="CUMPLE_06_ATC_PSICOTERAPIA_INTER_INDIV" dataDxfId="7"/>
+    <tableColumn id="20" name="Denominador" dataDxfId="6"/>
+    <tableColumn id="21" name="Numerador" dataDxfId="5"/>
+    <tableColumn id="22" name="Excluye" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -13378,10 +13366,10 @@
         <v>3</v>
       </c>
       <c r="O100" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P100" s="13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q100" s="13">
         <v>1</v>
@@ -14326,7 +14314,7 @@
         <v>3</v>
       </c>
       <c r="O114" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P114" s="13">
         <v>6</v>
@@ -17431,13 +17419,13 @@
         <v>46161</v>
       </c>
       <c r="N160" s="13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O160" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P160" s="13">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q160" s="13">
         <v>1</v>
